--- a/web_kit_learning_platform/assets/vocabulary_tmp.xlsx
+++ b/web_kit_learning_platform/assets/vocabulary_tmp.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Buixu\Projects\fft_projects\elearning\web_kit_learning_platform\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Buixu\OneDrive\Desktop\elearning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB16D8F6-8EEC-4476-9268-0B337E0A4712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A51B5B1-60FF-447A-8BEA-D881A8220260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B171B615-2220-4BA0-B451-FA9C688AC575}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>simplified</t>
   </si>
@@ -54,9 +54,6 @@
     <t>Giản thể</t>
   </si>
   <si>
-    <t>Phồn thể</t>
-  </si>
-  <si>
     <t>Phiên âm giản thể</t>
   </si>
   <si>
@@ -66,31 +63,28 @@
     <t>từ loại</t>
   </si>
   <si>
-    <t>Giản thể1</t>
-  </si>
-  <si>
-    <t>Phồn thể1</t>
-  </si>
-  <si>
-    <t>Phiên âm giản thể1</t>
-  </si>
-  <si>
-    <t>Nghĩa1</t>
-  </si>
-  <si>
-    <t>từ loại1</t>
-  </si>
-  <si>
     <t>STT</t>
   </si>
   <si>
     <t>audio</t>
   </si>
   <si>
-    <t>Giản thể.mp3</t>
-  </si>
-  <si>
-    <t>Giản thể1.mp3</t>
+    <t>Giản thể.WAV</t>
+  </si>
+  <si>
+    <t>example_simplified</t>
+  </si>
+  <si>
+    <t>example_pinyin_tones</t>
+  </si>
+  <si>
+    <t>example_translation_vn</t>
+  </si>
+  <si>
+    <t>example_audio</t>
+  </si>
+  <si>
+    <t>hán việt</t>
   </si>
 </sst>
 </file>
@@ -456,20 +450,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A30D3FE2-CA23-46D9-A8F6-5F0F450D381A}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="27.7109375" customWidth="1"/>
-    <col min="3" max="3" width="35.28515625" customWidth="1"/>
-    <col min="4" max="4" width="31.42578125" customWidth="1"/>
-    <col min="5" max="5" width="28.42578125" customWidth="1"/>
-    <col min="6" max="6" width="34.85546875" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
+    <col min="4" max="4" width="20.42578125" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" customWidth="1"/>
     <col min="7" max="7" width="44.7109375" customWidth="1"/>
+    <col min="8" max="8" width="22.28515625" customWidth="1"/>
+    <col min="9" max="9" width="24.140625" customWidth="1"/>
+    <col min="10" max="10" width="23.5703125" customWidth="1"/>
+    <col min="11" max="11" width="23.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -487,10 +485,22 @@
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -498,42 +508,31 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
       <c r="G2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>18</v>
+      <c r="H2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
